--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -4438,32 +4438,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548529</v>
+        <v>132548552</v>
       </c>
       <c r="B36" t="n">
-        <v>92352</v>
+        <v>80458</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530626</v>
+        <v>530696</v>
       </c>
       <c r="R36" t="n">
-        <v>6929494</v>
+        <v>6929348</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4545,10 +4545,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548535</v>
+        <v>132548575</v>
       </c>
       <c r="B37" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,42 +4556,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530649</v>
+        <v>530843</v>
       </c>
       <c r="R37" t="n">
-        <v>6929452</v>
+        <v>6929512</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4623,7 +4615,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4633,12 +4625,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,32 +4652,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548552</v>
+        <v>132548529</v>
       </c>
       <c r="B38" t="n">
-        <v>80458</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4700,13 +4687,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530696</v>
+        <v>530626</v>
       </c>
       <c r="R38" t="n">
-        <v>6929348</v>
+        <v>6929494</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4735,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4745,7 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,10 +4759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548575</v>
+        <v>132548535</v>
       </c>
       <c r="B39" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,34 +4770,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530843</v>
+        <v>530649</v>
       </c>
       <c r="R39" t="n">
-        <v>6929512</v>
+        <v>6929452</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4842,7 +4837,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4852,7 +4847,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -4438,32 +4438,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548552</v>
+        <v>132548529</v>
       </c>
       <c r="B36" t="n">
-        <v>80458</v>
+        <v>92352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530696</v>
+        <v>530626</v>
       </c>
       <c r="R36" t="n">
-        <v>6929348</v>
+        <v>6929494</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4545,10 +4545,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548575</v>
+        <v>132548535</v>
       </c>
       <c r="B37" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,34 +4556,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530843</v>
+        <v>530649</v>
       </c>
       <c r="R37" t="n">
-        <v>6929512</v>
+        <v>6929452</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4615,7 +4623,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4625,7 +4633,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,32 +4665,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548529</v>
+        <v>132548552</v>
       </c>
       <c r="B38" t="n">
-        <v>92352</v>
+        <v>80458</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4687,13 +4700,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530626</v>
+        <v>530696</v>
       </c>
       <c r="R38" t="n">
-        <v>6929494</v>
+        <v>6929348</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4735,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4745,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548535</v>
+        <v>132548575</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,42 +4783,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530649</v>
+        <v>530843</v>
       </c>
       <c r="R39" t="n">
-        <v>6929452</v>
+        <v>6929512</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4837,7 +4842,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4847,12 +4852,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132548548</v>
+        <v>132548580</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530675</v>
+        <v>530682</v>
       </c>
       <c r="R2" t="n">
-        <v>6929367</v>
+        <v>6929531</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Artbestämd genom mikroskopering</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132548558</v>
+        <v>132548542</v>
       </c>
       <c r="B3" t="n">
-        <v>58109</v>
+        <v>91898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,46 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530740</v>
+        <v>530678</v>
       </c>
       <c r="R3" t="n">
-        <v>6929375</v>
+        <v>6929444</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,48 +889,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132548542</v>
+        <v>132548548</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>92270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530678</v>
+        <v>530675</v>
       </c>
       <c r="R4" t="n">
-        <v>6929444</v>
+        <v>6929367</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +972,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,6 +986,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132548580</v>
+        <v>132548577</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,37 +1016,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530682</v>
+        <v>530789</v>
       </c>
       <c r="R5" t="n">
         <v>6929531</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1093,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132548577</v>
+        <v>132548558</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>58110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,29 +1136,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1167,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530789</v>
+        <v>530740</v>
       </c>
       <c r="R6" t="n">
-        <v>6929531</v>
+        <v>6929375</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132548583</v>
+        <v>132548533</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1255,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530643</v>
+        <v>530639</v>
       </c>
       <c r="R7" t="n">
-        <v>6929560</v>
+        <v>6929493</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132548530</v>
+        <v>132548583</v>
       </c>
       <c r="B8" t="n">
-        <v>92191</v>
+        <v>91898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530622</v>
+        <v>530643</v>
       </c>
       <c r="R8" t="n">
-        <v>6929498</v>
+        <v>6929560</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132548533</v>
+        <v>132548530</v>
       </c>
       <c r="B9" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,45 +1482,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530639</v>
+        <v>530622</v>
       </c>
       <c r="R9" t="n">
-        <v>6929493</v>
+        <v>6929498</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>132548581</v>
       </c>
       <c r="B10" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>132548566</v>
       </c>
       <c r="B11" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132548554</v>
+        <v>132548568</v>
       </c>
       <c r="B12" t="n">
-        <v>91892</v>
+        <v>91919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,21 +1803,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530690</v>
+        <v>530705</v>
       </c>
       <c r="R12" t="n">
-        <v>6929370</v>
+        <v>6929498</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132548568</v>
+        <v>132548554</v>
       </c>
       <c r="B13" t="n">
-        <v>91913</v>
+        <v>91898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530705</v>
+        <v>530690</v>
       </c>
       <c r="R13" t="n">
-        <v>6929498</v>
+        <v>6929370</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,7 +2009,7 @@
         <v>132548538</v>
       </c>
       <c r="B14" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>132548579</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132548557</v>
+        <v>132548537</v>
       </c>
       <c r="B16" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530725</v>
+        <v>530617</v>
       </c>
       <c r="R16" t="n">
-        <v>6929374</v>
+        <v>6929448</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132548555</v>
+        <v>132548528</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,45 +2351,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530722</v>
+        <v>530601</v>
       </c>
       <c r="R17" t="n">
-        <v>6929379</v>
+        <v>6929511</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,12 +2420,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132548537</v>
+        <v>132548557</v>
       </c>
       <c r="B18" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530617</v>
+        <v>530725</v>
       </c>
       <c r="R18" t="n">
-        <v>6929448</v>
+        <v>6929374</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2530,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132548528</v>
+        <v>132548555</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,37 +2565,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530601</v>
+        <v>530722</v>
       </c>
       <c r="R19" t="n">
-        <v>6929511</v>
+        <v>6929379</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,53 +2674,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132548565</v>
+        <v>132548534</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>97219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530777</v>
+        <v>530648</v>
       </c>
       <c r="R20" t="n">
-        <v>6929412</v>
+        <v>6929461</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -2752,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132548550</v>
+        <v>132548559</v>
       </c>
       <c r="B21" t="n">
-        <v>80422</v>
+        <v>57949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,37 +2792,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530694</v>
+        <v>530747</v>
       </c>
       <c r="R21" t="n">
-        <v>6929354</v>
+        <v>6929376</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2869,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132548559</v>
+        <v>132548565</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,16 +2912,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2939,13 +2944,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530747</v>
+        <v>530777</v>
       </c>
       <c r="R22" t="n">
-        <v>6929376</v>
+        <v>6929412</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2974,7 +2979,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2984,12 +2989,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,32 +3016,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132548534</v>
+        <v>132548550</v>
       </c>
       <c r="B23" t="n">
-        <v>97211</v>
+        <v>80424</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3051,13 +3051,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530648</v>
+        <v>530694</v>
       </c>
       <c r="R23" t="n">
-        <v>6929461</v>
+        <v>6929354</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,7 +3126,7 @@
         <v>132548584</v>
       </c>
       <c r="B24" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>132548527</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>132548536</v>
       </c>
       <c r="B26" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132548576</v>
+        <v>132548582</v>
       </c>
       <c r="B27" t="n">
-        <v>93180</v>
+        <v>91861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530800</v>
+        <v>530640</v>
       </c>
       <c r="R27" t="n">
-        <v>6929548</v>
+        <v>6929557</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132548563</v>
+        <v>132548572</v>
       </c>
       <c r="B28" t="n">
-        <v>57948</v>
+        <v>91919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,45 +3562,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530731</v>
+        <v>530821</v>
       </c>
       <c r="R28" t="n">
-        <v>6929406</v>
+        <v>6929517</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3629,7 +3621,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3639,12 +3631,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3674,7 +3661,7 @@
         <v>132548578</v>
       </c>
       <c r="B29" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,32 +3765,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132548572</v>
+        <v>132548576</v>
       </c>
       <c r="B30" t="n">
-        <v>91913</v>
+        <v>93186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3813,13 +3800,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530821</v>
+        <v>530800</v>
       </c>
       <c r="R30" t="n">
-        <v>6929517</v>
+        <v>6929548</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3848,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3858,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,48 +3872,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132548582</v>
+        <v>132548563</v>
       </c>
       <c r="B31" t="n">
-        <v>91855</v>
+        <v>57949</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>530640</v>
+        <v>530731</v>
       </c>
       <c r="R31" t="n">
-        <v>6929557</v>
+        <v>6929406</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3955,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3965,7 +3960,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3995,7 +3995,7 @@
         <v>132548564</v>
       </c>
       <c r="B32" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,48 +4104,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132548549</v>
+        <v>132548539</v>
       </c>
       <c r="B33" t="n">
-        <v>97211</v>
+        <v>57949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530679</v>
+        <v>530628</v>
       </c>
       <c r="R33" t="n">
-        <v>6929339</v>
+        <v>6929403</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4174,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4184,7 +4192,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4211,32 +4224,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132548546</v>
+        <v>132548549</v>
       </c>
       <c r="B34" t="n">
-        <v>92191</v>
+        <v>97219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4246,13 +4259,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530661</v>
+        <v>530679</v>
       </c>
       <c r="R34" t="n">
-        <v>6929368</v>
+        <v>6929339</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4281,7 +4294,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4291,7 +4304,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4318,10 +4331,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132548539</v>
+        <v>132548546</v>
       </c>
       <c r="B35" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4329,42 +4342,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530628</v>
+        <v>530661</v>
       </c>
       <c r="R35" t="n">
-        <v>6929403</v>
+        <v>6929368</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4396,7 +4401,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4406,12 +4411,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4441,7 +4441,7 @@
         <v>132548529</v>
       </c>
       <c r="B36" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548535</v>
+        <v>132548575</v>
       </c>
       <c r="B37" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,42 +4556,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530649</v>
+        <v>530843</v>
       </c>
       <c r="R37" t="n">
-        <v>6929452</v>
+        <v>6929512</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4623,7 +4615,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4633,12 +4625,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4668,7 +4655,7 @@
         <v>132548552</v>
       </c>
       <c r="B38" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4772,10 +4759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548575</v>
+        <v>132548535</v>
       </c>
       <c r="B39" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,34 +4770,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530843</v>
+        <v>530649</v>
       </c>
       <c r="R39" t="n">
-        <v>6929512</v>
+        <v>6929452</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4842,7 +4837,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4852,7 +4847,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132548531</v>
+        <v>132548545</v>
       </c>
       <c r="B40" t="n">
-        <v>91892</v>
+        <v>97219</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4914,13 +4914,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530623</v>
+        <v>530665</v>
       </c>
       <c r="R40" t="n">
-        <v>6929499</v>
+        <v>6929410</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4986,32 +4986,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132548545</v>
+        <v>132548531</v>
       </c>
       <c r="B41" t="n">
-        <v>97211</v>
+        <v>91898</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530665</v>
+        <v>530623</v>
       </c>
       <c r="R41" t="n">
-        <v>6929410</v>
+        <v>6929499</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,53 +5093,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132548543</v>
+        <v>132548553</v>
       </c>
       <c r="B42" t="n">
-        <v>57948</v>
+        <v>80328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530691</v>
+        <v>530693</v>
       </c>
       <c r="R42" t="n">
-        <v>6929458</v>
+        <v>6929364</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5171,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5181,12 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5213,10 +5200,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132548574</v>
+        <v>132548543</v>
       </c>
       <c r="B43" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5224,34 +5211,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530833</v>
+        <v>530691</v>
       </c>
       <c r="R43" t="n">
-        <v>6929513</v>
+        <v>6929458</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5283,7 +5278,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5293,7 +5288,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5320,10 +5320,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132548541</v>
+        <v>132548574</v>
       </c>
       <c r="B44" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530677</v>
+        <v>530833</v>
       </c>
       <c r="R44" t="n">
-        <v>6929443</v>
+        <v>6929513</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132548556</v>
+        <v>132548541</v>
       </c>
       <c r="B45" t="n">
-        <v>91892</v>
+        <v>92197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5438,21 +5438,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530727</v>
+        <v>530677</v>
       </c>
       <c r="R45" t="n">
-        <v>6929373</v>
+        <v>6929443</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5534,32 +5534,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132548553</v>
+        <v>132548556</v>
       </c>
       <c r="B46" t="n">
-        <v>80326</v>
+        <v>91898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>530693</v>
+        <v>530727</v>
       </c>
       <c r="R46" t="n">
-        <v>6929364</v>
+        <v>6929373</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5644,7 +5644,7 @@
         <v>132548544</v>
       </c>
       <c r="B47" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>132548540</v>
       </c>
       <c r="B48" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>132548547</v>
       </c>
       <c r="B49" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -2674,32 +2674,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132548534</v>
+        <v>132548550</v>
       </c>
       <c r="B20" t="n">
-        <v>97219</v>
+        <v>80424</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,13 +2709,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530648</v>
+        <v>530694</v>
       </c>
       <c r="R20" t="n">
-        <v>6929461</v>
+        <v>6929354</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3016,32 +3016,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132548550</v>
+        <v>132548534</v>
       </c>
       <c r="B23" t="n">
-        <v>80424</v>
+        <v>97219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3051,13 +3051,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530694</v>
+        <v>530648</v>
       </c>
       <c r="R23" t="n">
-        <v>6929354</v>
+        <v>6929461</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4438,48 +4438,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548529</v>
+        <v>132548535</v>
       </c>
       <c r="B36" t="n">
-        <v>92358</v>
+        <v>57949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530626</v>
+        <v>530649</v>
       </c>
       <c r="R36" t="n">
-        <v>6929494</v>
+        <v>6929452</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4516,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4526,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4545,32 +4558,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548575</v>
+        <v>132548552</v>
       </c>
       <c r="B37" t="n">
-        <v>92197</v>
+        <v>80460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4593,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530843</v>
+        <v>530696</v>
       </c>
       <c r="R37" t="n">
-        <v>6929512</v>
+        <v>6929348</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4615,7 +4628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4625,7 +4638,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,32 +4665,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548552</v>
+        <v>132548529</v>
       </c>
       <c r="B38" t="n">
-        <v>80460</v>
+        <v>92358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4687,13 +4700,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530696</v>
+        <v>530626</v>
       </c>
       <c r="R38" t="n">
-        <v>6929348</v>
+        <v>6929494</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4735,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4745,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548535</v>
+        <v>132548575</v>
       </c>
       <c r="B39" t="n">
-        <v>57949</v>
+        <v>92197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,42 +4783,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530649</v>
+        <v>530843</v>
       </c>
       <c r="R39" t="n">
-        <v>6929452</v>
+        <v>6929512</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4837,7 +4842,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4847,12 +4852,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132548553</v>
+        <v>132548574</v>
       </c>
       <c r="B42" t="n">
-        <v>80328</v>
+        <v>92197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530693</v>
+        <v>530833</v>
       </c>
       <c r="R42" t="n">
-        <v>6929364</v>
+        <v>6929513</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,10 +5200,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132548543</v>
+        <v>132548541</v>
       </c>
       <c r="B43" t="n">
-        <v>57949</v>
+        <v>92197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,45 +5211,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530691</v>
+        <v>530677</v>
       </c>
       <c r="R43" t="n">
-        <v>6929458</v>
+        <v>6929443</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5278,7 +5270,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5288,12 +5280,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5320,10 +5307,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132548574</v>
+        <v>132548556</v>
       </c>
       <c r="B44" t="n">
-        <v>92197</v>
+        <v>91898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5331,21 +5318,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5355,10 +5342,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530833</v>
+        <v>530727</v>
       </c>
       <c r="R44" t="n">
-        <v>6929513</v>
+        <v>6929373</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5390,7 +5377,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5400,7 +5387,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5427,32 +5414,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132548541</v>
+        <v>132548553</v>
       </c>
       <c r="B45" t="n">
-        <v>92197</v>
+        <v>80328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5462,13 +5449,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530677</v>
+        <v>530693</v>
       </c>
       <c r="R45" t="n">
-        <v>6929443</v>
+        <v>6929364</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5497,7 +5484,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5507,7 +5494,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5534,10 +5521,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132548556</v>
+        <v>132548543</v>
       </c>
       <c r="B46" t="n">
-        <v>91898</v>
+        <v>57949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5545,34 +5532,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>530727</v>
+        <v>530691</v>
       </c>
       <c r="R46" t="n">
-        <v>6929373</v>
+        <v>6929458</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5604,7 +5599,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5614,7 +5609,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132548580</v>
+        <v>132548577</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530682</v>
+        <v>530789</v>
       </c>
       <c r="R2" t="n">
         <v>6929531</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +798,7 @@
         <v>132548542</v>
       </c>
       <c r="B3" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +905,7 @@
         <v>132548548</v>
       </c>
       <c r="B4" t="n">
-        <v>92270</v>
+        <v>92280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132548577</v>
+        <v>132548580</v>
       </c>
       <c r="B5" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,45 +1029,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530789</v>
+        <v>530682</v>
       </c>
       <c r="R5" t="n">
         <v>6929531</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,12 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
         <v>132548558</v>
       </c>
       <c r="B6" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132548533</v>
+        <v>132548583</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,45 +1255,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530639</v>
+        <v>530643</v>
       </c>
       <c r="R7" t="n">
-        <v>6929493</v>
+        <v>6929560</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132548583</v>
+        <v>132548530</v>
       </c>
       <c r="B8" t="n">
-        <v>91898</v>
+        <v>92207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,21 +1362,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530643</v>
+        <v>530622</v>
       </c>
       <c r="R8" t="n">
-        <v>6929560</v>
+        <v>6929498</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132548530</v>
+        <v>132548533</v>
       </c>
       <c r="B9" t="n">
-        <v>92197</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,37 +1469,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530622</v>
+        <v>530639</v>
       </c>
       <c r="R9" t="n">
-        <v>6929498</v>
+        <v>6929493</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>132548581</v>
       </c>
       <c r="B10" t="n">
-        <v>80452</v>
+        <v>80460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>132548566</v>
       </c>
       <c r="B11" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>132548568</v>
       </c>
       <c r="B12" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>132548554</v>
       </c>
       <c r="B13" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>132548538</v>
       </c>
       <c r="B14" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>132548579</v>
       </c>
       <c r="B15" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>132548537</v>
       </c>
       <c r="B16" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>132548528</v>
       </c>
       <c r="B17" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132548557</v>
       </c>
       <c r="B18" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>132548555</v>
       </c>
       <c r="B19" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132548550</v>
+        <v>132548559</v>
       </c>
       <c r="B20" t="n">
-        <v>80424</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,37 +2685,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530694</v>
+        <v>530747</v>
       </c>
       <c r="R20" t="n">
-        <v>6929354</v>
+        <v>6929376</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,7 +2752,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2762,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,56 +2794,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132548559</v>
+        <v>132548534</v>
       </c>
       <c r="B21" t="n">
-        <v>57949</v>
+        <v>97229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530747</v>
+        <v>530648</v>
       </c>
       <c r="R21" t="n">
-        <v>6929376</v>
+        <v>6929461</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2864,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,12 +2874,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132548565</v>
+        <v>132548550</v>
       </c>
       <c r="B22" t="n">
-        <v>57946</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,45 +2912,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530777</v>
+        <v>530694</v>
       </c>
       <c r="R22" t="n">
-        <v>6929412</v>
+        <v>6929354</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2979,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2989,7 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,45 +3008,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132548534</v>
+        <v>132548565</v>
       </c>
       <c r="B23" t="n">
-        <v>97219</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530648</v>
+        <v>530777</v>
       </c>
       <c r="R23" t="n">
-        <v>6929461</v>
+        <v>6929412</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,7 +3126,7 @@
         <v>132548584</v>
       </c>
       <c r="B24" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>132548527</v>
       </c>
       <c r="B25" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>132548536</v>
       </c>
       <c r="B26" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3444,48 +3444,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132548582</v>
+        <v>132548563</v>
       </c>
       <c r="B27" t="n">
-        <v>91861</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530640</v>
+        <v>530731</v>
       </c>
       <c r="R27" t="n">
-        <v>6929557</v>
+        <v>6929406</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,7 +3522,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,7 +3532,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3551,32 +3564,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132548572</v>
+        <v>132548582</v>
       </c>
       <c r="B28" t="n">
-        <v>91919</v>
+        <v>91871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3586,13 +3599,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530821</v>
+        <v>530640</v>
       </c>
       <c r="R28" t="n">
-        <v>6929517</v>
+        <v>6929557</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3621,7 +3634,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3631,7 +3644,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3658,10 +3671,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132548578</v>
+        <v>132548572</v>
       </c>
       <c r="B29" t="n">
-        <v>92197</v>
+        <v>91929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,21 +3682,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3693,13 +3706,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>530803</v>
+        <v>530821</v>
       </c>
       <c r="R29" t="n">
-        <v>6929516</v>
+        <v>6929517</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3728,7 +3741,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3738,7 +3751,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3765,32 +3778,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132548576</v>
+        <v>132548578</v>
       </c>
       <c r="B30" t="n">
-        <v>93186</v>
+        <v>92207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3813,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530800</v>
+        <v>530803</v>
       </c>
       <c r="R30" t="n">
-        <v>6929548</v>
+        <v>6929516</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3835,7 +3848,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3845,7 +3858,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3872,53 +3885,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132548563</v>
+        <v>132548576</v>
       </c>
       <c r="B31" t="n">
-        <v>57949</v>
+        <v>93196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>530731</v>
+        <v>530800</v>
       </c>
       <c r="R31" t="n">
-        <v>6929406</v>
+        <v>6929548</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3950,7 +3955,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,12 +3965,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3995,7 +3995,7 @@
         <v>132548564</v>
       </c>
       <c r="B32" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>132548539</v>
       </c>
       <c r="B33" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>132548549</v>
       </c>
       <c r="B34" t="n">
-        <v>97219</v>
+        <v>97229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>132548546</v>
       </c>
       <c r="B35" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4438,56 +4438,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548535</v>
+        <v>132548529</v>
       </c>
       <c r="B36" t="n">
-        <v>57949</v>
+        <v>92368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530649</v>
+        <v>530626</v>
       </c>
       <c r="R36" t="n">
-        <v>6929452</v>
+        <v>6929494</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4516,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4526,12 +4518,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4558,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548552</v>
+        <v>132548575</v>
       </c>
       <c r="B37" t="n">
-        <v>80460</v>
+        <v>92207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4593,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530696</v>
+        <v>530843</v>
       </c>
       <c r="R37" t="n">
-        <v>6929348</v>
+        <v>6929512</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4628,7 +4615,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4638,7 +4625,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,32 +4652,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548529</v>
+        <v>132548552</v>
       </c>
       <c r="B38" t="n">
-        <v>92358</v>
+        <v>80468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4700,13 +4687,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530626</v>
+        <v>530696</v>
       </c>
       <c r="R38" t="n">
-        <v>6929494</v>
+        <v>6929348</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4735,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4745,7 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,10 +4759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548575</v>
+        <v>132548535</v>
       </c>
       <c r="B39" t="n">
-        <v>92197</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,34 +4770,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530843</v>
+        <v>530649</v>
       </c>
       <c r="R39" t="n">
-        <v>6929512</v>
+        <v>6929452</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4842,7 +4837,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4852,7 +4847,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,7 +4882,7 @@
         <v>132548545</v>
       </c>
       <c r="B40" t="n">
-        <v>97219</v>
+        <v>97229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>132548531</v>
       </c>
       <c r="B41" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132548574</v>
+        <v>132548553</v>
       </c>
       <c r="B42" t="n">
-        <v>92197</v>
+        <v>80336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530833</v>
+        <v>530693</v>
       </c>
       <c r="R42" t="n">
-        <v>6929513</v>
+        <v>6929364</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,10 +5200,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132548541</v>
+        <v>132548574</v>
       </c>
       <c r="B43" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530677</v>
+        <v>530833</v>
       </c>
       <c r="R43" t="n">
-        <v>6929443</v>
+        <v>6929513</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132548556</v>
+        <v>132548541</v>
       </c>
       <c r="B44" t="n">
-        <v>91898</v>
+        <v>92207</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5318,21 +5318,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530727</v>
+        <v>530677</v>
       </c>
       <c r="R44" t="n">
-        <v>6929373</v>
+        <v>6929443</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5414,32 +5414,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132548553</v>
+        <v>132548556</v>
       </c>
       <c r="B45" t="n">
-        <v>80328</v>
+        <v>91908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530693</v>
+        <v>530727</v>
       </c>
       <c r="R45" t="n">
-        <v>6929364</v>
+        <v>6929373</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5524,7 +5524,7 @@
         <v>132548543</v>
       </c>
       <c r="B46" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>132548544</v>
       </c>
       <c r="B47" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>132548540</v>
       </c>
       <c r="B48" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>132548547</v>
       </c>
       <c r="B49" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132548577</v>
+        <v>132548542</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530789</v>
+        <v>530678</v>
       </c>
       <c r="R2" t="n">
-        <v>6929531</v>
+        <v>6929444</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,48 +782,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132548542</v>
+        <v>132548548</v>
       </c>
       <c r="B3" t="n">
-        <v>91908</v>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530678</v>
+        <v>530675</v>
       </c>
       <c r="R3" t="n">
-        <v>6929444</v>
+        <v>6929367</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +865,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,51 +898,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132548548</v>
+        <v>132548580</v>
       </c>
       <c r="B4" t="n">
-        <v>92280</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530675</v>
+        <v>530682</v>
       </c>
       <c r="R4" t="n">
-        <v>6929367</v>
+        <v>6929531</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,12 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämd genom mikroskopering</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132548580</v>
+        <v>132548577</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,37 +1016,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530682</v>
+        <v>530789</v>
       </c>
       <c r="R5" t="n">
         <v>6929531</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1093,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132548583</v>
+        <v>132548533</v>
       </c>
       <c r="B7" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1255,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530643</v>
+        <v>530639</v>
       </c>
       <c r="R7" t="n">
-        <v>6929560</v>
+        <v>6929493</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1367,7 @@
         <v>132548530</v>
       </c>
       <c r="B8" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132548533</v>
+        <v>132548583</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,45 +1482,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530639</v>
+        <v>530643</v>
       </c>
       <c r="R9" t="n">
-        <v>6929493</v>
+        <v>6929560</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,32 +1578,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132548581</v>
+        <v>132548566</v>
       </c>
       <c r="B10" t="n">
-        <v>80460</v>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530680</v>
+        <v>530798</v>
       </c>
       <c r="R10" t="n">
-        <v>6929528</v>
+        <v>6929445</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132548566</v>
+        <v>132548581</v>
       </c>
       <c r="B11" t="n">
-        <v>92368</v>
+        <v>80460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530798</v>
+        <v>530680</v>
       </c>
       <c r="R11" t="n">
-        <v>6929445</v>
+        <v>6929528</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
         <v>132548568</v>
       </c>
       <c r="B12" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>132548554</v>
       </c>
       <c r="B13" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>132548538</v>
       </c>
       <c r="B14" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132548537</v>
+        <v>132548555</v>
       </c>
       <c r="B16" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,37 +2244,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530617</v>
+        <v>530722</v>
       </c>
       <c r="R16" t="n">
-        <v>6929448</v>
+        <v>6929379</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2321,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132548528</v>
+        <v>132548537</v>
       </c>
       <c r="B17" t="n">
-        <v>91908</v>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,21 +2364,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,13 +2388,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530601</v>
+        <v>530617</v>
       </c>
       <c r="R17" t="n">
-        <v>6929511</v>
+        <v>6929448</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,7 +2463,7 @@
         <v>132548557</v>
       </c>
       <c r="B18" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132548555</v>
+        <v>132548528</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2565,45 +2578,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530722</v>
+        <v>530601</v>
       </c>
       <c r="R19" t="n">
-        <v>6929379</v>
+        <v>6929511</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132548559</v>
+        <v>132548550</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,45 +2685,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530747</v>
+        <v>530694</v>
       </c>
       <c r="R20" t="n">
-        <v>6929376</v>
+        <v>6929354</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,12 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,7 +2784,7 @@
         <v>132548534</v>
       </c>
       <c r="B21" t="n">
-        <v>97229</v>
+        <v>97230</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132548550</v>
+        <v>132548559</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,37 +2899,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530694</v>
+        <v>530747</v>
       </c>
       <c r="R22" t="n">
-        <v>6929354</v>
+        <v>6929376</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,32 +3123,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132548584</v>
+        <v>132548527</v>
       </c>
       <c r="B24" t="n">
-        <v>92368</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530636</v>
+        <v>530559</v>
       </c>
       <c r="R24" t="n">
-        <v>6929549</v>
+        <v>6929534</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,32 +3230,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132548527</v>
+        <v>132548584</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530559</v>
+        <v>530636</v>
       </c>
       <c r="R25" t="n">
-        <v>6929534</v>
+        <v>6929549</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3340,7 +3340,7 @@
         <v>132548536</v>
       </c>
       <c r="B26" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132548563</v>
+        <v>132548578</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,42 +3455,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530731</v>
+        <v>530803</v>
       </c>
       <c r="R27" t="n">
-        <v>6929406</v>
+        <v>6929516</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3522,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3532,12 +3524,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,7 +3554,7 @@
         <v>132548582</v>
       </c>
       <c r="B28" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3674,7 +3661,7 @@
         <v>132548572</v>
       </c>
       <c r="B29" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,32 +3765,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132548578</v>
+        <v>132548576</v>
       </c>
       <c r="B30" t="n">
-        <v>92207</v>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3813,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530803</v>
+        <v>530800</v>
       </c>
       <c r="R30" t="n">
-        <v>6929516</v>
+        <v>6929548</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3848,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3858,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,45 +3872,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132548576</v>
+        <v>132548563</v>
       </c>
       <c r="B31" t="n">
-        <v>93196</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>530800</v>
+        <v>530731</v>
       </c>
       <c r="R31" t="n">
-        <v>6929548</v>
+        <v>6929406</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3955,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3965,7 +3960,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3995,7 +3995,7 @@
         <v>132548564</v>
       </c>
       <c r="B32" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132548539</v>
+        <v>132548546</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4115,42 +4115,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530628</v>
+        <v>530661</v>
       </c>
       <c r="R33" t="n">
-        <v>6929403</v>
+        <v>6929368</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4182,7 +4174,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,12 +4184,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4227,7 +4214,7 @@
         <v>132548549</v>
       </c>
       <c r="B34" t="n">
-        <v>97229</v>
+        <v>97230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4331,10 +4318,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132548546</v>
+        <v>132548539</v>
       </c>
       <c r="B35" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,34 +4329,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530661</v>
+        <v>530628</v>
       </c>
       <c r="R35" t="n">
-        <v>6929368</v>
+        <v>6929403</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4401,7 +4396,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4411,7 +4406,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4438,48 +4438,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548529</v>
+        <v>132548535</v>
       </c>
       <c r="B36" t="n">
-        <v>92368</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530626</v>
+        <v>530649</v>
       </c>
       <c r="R36" t="n">
-        <v>6929494</v>
+        <v>6929452</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4516,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4526,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4548,7 +4561,7 @@
         <v>132548575</v>
       </c>
       <c r="B37" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4652,32 +4665,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548552</v>
+        <v>132548529</v>
       </c>
       <c r="B38" t="n">
-        <v>80468</v>
+        <v>92369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4687,13 +4700,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530696</v>
+        <v>530626</v>
       </c>
       <c r="R38" t="n">
-        <v>6929348</v>
+        <v>6929494</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4735,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4745,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,53 +4772,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548535</v>
+        <v>132548552</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530649</v>
+        <v>530696</v>
       </c>
       <c r="R39" t="n">
-        <v>6929452</v>
+        <v>6929348</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4837,7 +4842,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4847,12 +4852,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,7 +4882,7 @@
         <v>132548545</v>
       </c>
       <c r="B40" t="n">
-        <v>97229</v>
+        <v>97230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>132548531</v>
       </c>
       <c r="B41" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132548553</v>
+        <v>132548541</v>
       </c>
       <c r="B42" t="n">
-        <v>80336</v>
+        <v>92208</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530693</v>
+        <v>530677</v>
       </c>
       <c r="R42" t="n">
-        <v>6929364</v>
+        <v>6929443</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5203,7 +5203,7 @@
         <v>132548574</v>
       </c>
       <c r="B43" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5307,32 +5307,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132548541</v>
+        <v>132548553</v>
       </c>
       <c r="B44" t="n">
-        <v>92207</v>
+        <v>80336</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530677</v>
+        <v>530693</v>
       </c>
       <c r="R44" t="n">
-        <v>6929443</v>
+        <v>6929364</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,7 +5417,7 @@
         <v>132548556</v>
       </c>
       <c r="B45" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>132548540</v>
       </c>
       <c r="B48" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>132548547</v>
       </c>
       <c r="B49" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132548580</v>
+        <v>132548542</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530682</v>
+        <v>530678</v>
       </c>
       <c r="R2" t="n">
-        <v>6929531</v>
+        <v>6929444</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132548542</v>
+        <v>132548548</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>92290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530678</v>
+        <v>530675</v>
       </c>
       <c r="R3" t="n">
-        <v>6929444</v>
+        <v>6929367</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +865,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,37 +898,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132548548</v>
+        <v>132548577</v>
       </c>
       <c r="B4" t="n">
-        <v>92290</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530675</v>
+        <v>530789</v>
       </c>
       <c r="R4" t="n">
-        <v>6929367</v>
+        <v>6929531</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,12 +986,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Artbestämd genom mikroskopering</t>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +1000,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132548577</v>
+        <v>132548558</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>58119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,29 +1029,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1048,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530789</v>
+        <v>530740</v>
       </c>
       <c r="R5" t="n">
-        <v>6929531</v>
+        <v>6929375</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132548558</v>
+        <v>132548580</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,46 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530740</v>
+        <v>530682</v>
       </c>
       <c r="R6" t="n">
-        <v>6929375</v>
+        <v>6929531</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132548533</v>
+        <v>132548583</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,45 +1255,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530639</v>
+        <v>530643</v>
       </c>
       <c r="R7" t="n">
-        <v>6929493</v>
+        <v>6929560</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132548583</v>
+        <v>132548530</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,21 +1362,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530643</v>
+        <v>530622</v>
       </c>
       <c r="R8" t="n">
-        <v>6929560</v>
+        <v>6929498</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132548530</v>
+        <v>132548533</v>
       </c>
       <c r="B9" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,37 +1469,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530622</v>
+        <v>530639</v>
       </c>
       <c r="R9" t="n">
-        <v>6929498</v>
+        <v>6929493</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,32 +1578,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132548581</v>
+        <v>132548566</v>
       </c>
       <c r="B10" t="n">
-        <v>80466</v>
+        <v>92378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530680</v>
+        <v>530798</v>
       </c>
       <c r="R10" t="n">
-        <v>6929528</v>
+        <v>6929445</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132548566</v>
+        <v>132548581</v>
       </c>
       <c r="B11" t="n">
-        <v>92378</v>
+        <v>80466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530798</v>
+        <v>530680</v>
       </c>
       <c r="R11" t="n">
-        <v>6929445</v>
+        <v>6929528</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2674,45 +2674,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132548534</v>
+        <v>132548565</v>
       </c>
       <c r="B20" t="n">
-        <v>97243</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530648</v>
+        <v>530777</v>
       </c>
       <c r="R20" t="n">
-        <v>6929461</v>
+        <v>6929412</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -2744,7 +2752,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2762,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132548565</v>
+        <v>132548550</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>80438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,45 +2800,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530777</v>
+        <v>530694</v>
       </c>
       <c r="R21" t="n">
-        <v>6929412</v>
+        <v>6929354</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,32 +2896,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132548550</v>
+        <v>132548534</v>
       </c>
       <c r="B22" t="n">
-        <v>80438</v>
+        <v>97243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530694</v>
+        <v>530648</v>
       </c>
       <c r="R22" t="n">
-        <v>6929354</v>
+        <v>6929461</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3444,56 +3444,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132548563</v>
+        <v>132548582</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530731</v>
+        <v>530640</v>
       </c>
       <c r="R27" t="n">
-        <v>6929406</v>
+        <v>6929557</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3522,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3532,12 +3524,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,32 +3551,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132548582</v>
+        <v>132548572</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>91939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3599,13 +3586,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530640</v>
+        <v>530821</v>
       </c>
       <c r="R28" t="n">
-        <v>6929557</v>
+        <v>6929517</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3634,7 +3621,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3644,7 +3631,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,10 +3658,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132548572</v>
+        <v>132548578</v>
       </c>
       <c r="B29" t="n">
-        <v>91939</v>
+        <v>92217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,21 +3669,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3706,13 +3693,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>530821</v>
+        <v>530803</v>
       </c>
       <c r="R29" t="n">
-        <v>6929517</v>
+        <v>6929516</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3741,7 +3728,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3751,7 +3738,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,32 +3765,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132548578</v>
+        <v>132548576</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>93206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3813,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530803</v>
+        <v>530800</v>
       </c>
       <c r="R30" t="n">
-        <v>6929516</v>
+        <v>6929548</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3848,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3858,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,45 +3872,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132548576</v>
+        <v>132548563</v>
       </c>
       <c r="B31" t="n">
-        <v>93206</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>530800</v>
+        <v>530731</v>
       </c>
       <c r="R31" t="n">
-        <v>6929548</v>
+        <v>6929406</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3955,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3965,7 +3960,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,48 +4104,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132548549</v>
+        <v>132548539</v>
       </c>
       <c r="B33" t="n">
-        <v>97243</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530679</v>
+        <v>530628</v>
       </c>
       <c r="R33" t="n">
-        <v>6929339</v>
+        <v>6929403</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4174,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4184,7 +4192,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4211,32 +4224,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132548546</v>
+        <v>132548549</v>
       </c>
       <c r="B34" t="n">
-        <v>92217</v>
+        <v>97243</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4246,13 +4259,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530661</v>
+        <v>530679</v>
       </c>
       <c r="R34" t="n">
-        <v>6929368</v>
+        <v>6929339</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4281,7 +4294,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4291,7 +4304,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4318,10 +4331,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132548539</v>
+        <v>132548546</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4329,42 +4342,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530628</v>
+        <v>530661</v>
       </c>
       <c r="R35" t="n">
-        <v>6929403</v>
+        <v>6929368</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4396,7 +4401,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4406,12 +4411,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4438,32 +4438,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548552</v>
+        <v>132548529</v>
       </c>
       <c r="B36" t="n">
-        <v>80474</v>
+        <v>92378</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530696</v>
+        <v>530626</v>
       </c>
       <c r="R36" t="n">
-        <v>6929348</v>
+        <v>6929494</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548529</v>
+        <v>132548575</v>
       </c>
       <c r="B37" t="n">
-        <v>92378</v>
+        <v>92217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530626</v>
+        <v>530843</v>
       </c>
       <c r="R37" t="n">
-        <v>6929494</v>
+        <v>6929512</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,32 +4652,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548575</v>
+        <v>132548552</v>
       </c>
       <c r="B38" t="n">
-        <v>92217</v>
+        <v>80474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530843</v>
+        <v>530696</v>
       </c>
       <c r="R38" t="n">
-        <v>6929512</v>
+        <v>6929348</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5213,32 +5213,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132548553</v>
+        <v>132548574</v>
       </c>
       <c r="B43" t="n">
-        <v>80342</v>
+        <v>92217</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530693</v>
+        <v>530833</v>
       </c>
       <c r="R43" t="n">
-        <v>6929364</v>
+        <v>6929513</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5320,7 +5320,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132548574</v>
+        <v>132548541</v>
       </c>
       <c r="B44" t="n">
         <v>92217</v>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530833</v>
+        <v>530677</v>
       </c>
       <c r="R44" t="n">
-        <v>6929513</v>
+        <v>6929443</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132548541</v>
+        <v>132548556</v>
       </c>
       <c r="B45" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5438,21 +5438,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530677</v>
+        <v>530727</v>
       </c>
       <c r="R45" t="n">
-        <v>6929443</v>
+        <v>6929373</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5534,32 +5534,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132548556</v>
+        <v>132548553</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>80342</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>530727</v>
+        <v>530693</v>
       </c>
       <c r="R46" t="n">
-        <v>6929373</v>
+        <v>6929364</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 23035-2024 artfynd.xlsx
+++ b/artfynd/A 23035-2024 artfynd.xlsx
@@ -782,51 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132548548</v>
+        <v>132548580</v>
       </c>
       <c r="B3" t="n">
-        <v>92290</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530675</v>
+        <v>530682</v>
       </c>
       <c r="R3" t="n">
-        <v>6929367</v>
+        <v>6929531</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Artbestämd genom mikroskopering</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1137,48 +1128,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132548580</v>
+        <v>132548548</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>92290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530682</v>
+        <v>530675</v>
       </c>
       <c r="R6" t="n">
-        <v>6929531</v>
+        <v>6929367</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,6 +1225,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132548583</v>
+        <v>132548533</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1255,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530643</v>
+        <v>530639</v>
       </c>
       <c r="R7" t="n">
-        <v>6929560</v>
+        <v>6929493</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132548530</v>
+        <v>132548583</v>
       </c>
       <c r="B8" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530622</v>
+        <v>530643</v>
       </c>
       <c r="R8" t="n">
-        <v>6929498</v>
+        <v>6929560</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132548533</v>
+        <v>132548530</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,45 +1482,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530639</v>
+        <v>530622</v>
       </c>
       <c r="R9" t="n">
-        <v>6929493</v>
+        <v>6929498</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132548565</v>
+        <v>132548559</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,16 +2685,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530777</v>
+        <v>530747</v>
       </c>
       <c r="R20" t="n">
-        <v>6929412</v>
+        <v>6929376</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2762,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3003,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132548559</v>
+        <v>132548565</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,16 +3019,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3046,13 +3051,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530747</v>
+        <v>530777</v>
       </c>
       <c r="R23" t="n">
-        <v>6929376</v>
+        <v>6929412</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,12 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två påbörjade bohål i tajgagrantickerötad gran. Hålen sitter omkring 1-1.5 meter ovan mark. Hålen är prydligt uthackade, men saknar bohålskammare. Biotopen är lämplig för arten.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3123,32 +3123,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132548584</v>
+        <v>132548527</v>
       </c>
       <c r="B24" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530636</v>
+        <v>530559</v>
       </c>
       <c r="R24" t="n">
-        <v>6929549</v>
+        <v>6929534</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,32 +3230,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132548527</v>
+        <v>132548584</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530559</v>
+        <v>530636</v>
       </c>
       <c r="R25" t="n">
-        <v>6929534</v>
+        <v>6929549</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132548578</v>
+        <v>132548576</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>93206</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>530803</v>
+        <v>530800</v>
       </c>
       <c r="R29" t="n">
-        <v>6929516</v>
+        <v>6929548</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3765,32 +3765,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132548576</v>
+        <v>132548578</v>
       </c>
       <c r="B30" t="n">
-        <v>93206</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530800</v>
+        <v>530803</v>
       </c>
       <c r="R30" t="n">
-        <v>6929548</v>
+        <v>6929516</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4104,10 +4104,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132548539</v>
+        <v>132548546</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4115,42 +4115,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530628</v>
+        <v>530661</v>
       </c>
       <c r="R33" t="n">
-        <v>6929403</v>
+        <v>6929368</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4182,7 +4174,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,12 +4184,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4331,10 +4318,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132548546</v>
+        <v>132548539</v>
       </c>
       <c r="B35" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,34 +4329,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530661</v>
+        <v>530628</v>
       </c>
       <c r="R35" t="n">
-        <v>6929368</v>
+        <v>6929403</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4401,7 +4396,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4411,7 +4406,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4438,32 +4438,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132548529</v>
+        <v>132548552</v>
       </c>
       <c r="B36" t="n">
-        <v>92378</v>
+        <v>80474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>530626</v>
+        <v>530696</v>
       </c>
       <c r="R36" t="n">
-        <v>6929494</v>
+        <v>6929348</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4545,10 +4545,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132548575</v>
+        <v>132548535</v>
       </c>
       <c r="B37" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,34 +4556,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530843</v>
+        <v>530649</v>
       </c>
       <c r="R37" t="n">
-        <v>6929512</v>
+        <v>6929452</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4615,7 +4623,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4625,7 +4633,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,32 +4665,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132548552</v>
+        <v>132548529</v>
       </c>
       <c r="B38" t="n">
-        <v>80474</v>
+        <v>92378</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4687,13 +4700,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530696</v>
+        <v>530626</v>
       </c>
       <c r="R38" t="n">
-        <v>6929348</v>
+        <v>6929494</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4735,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4745,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132548535</v>
+        <v>132548575</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,42 +4783,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530649</v>
+        <v>530843</v>
       </c>
       <c r="R39" t="n">
-        <v>6929452</v>
+        <v>6929512</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4837,7 +4842,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4847,12 +4852,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132548545</v>
+        <v>132548531</v>
       </c>
       <c r="B40" t="n">
-        <v>97243</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4914,13 +4914,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530665</v>
+        <v>530623</v>
       </c>
       <c r="R40" t="n">
-        <v>6929410</v>
+        <v>6929499</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4986,32 +4986,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132548531</v>
+        <v>132548545</v>
       </c>
       <c r="B41" t="n">
-        <v>91918</v>
+        <v>97243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530623</v>
+        <v>530665</v>
       </c>
       <c r="R41" t="n">
-        <v>6929499</v>
+        <v>6929410</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,53 +5093,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132548543</v>
+        <v>132548553</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>80342</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530691</v>
+        <v>530693</v>
       </c>
       <c r="R42" t="n">
-        <v>6929458</v>
+        <v>6929364</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5171,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5181,12 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5213,10 +5200,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132548574</v>
+        <v>132548543</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5224,34 +5211,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Råsjöån, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530833</v>
+        <v>530691</v>
       </c>
       <c r="R43" t="n">
-        <v>6929513</v>
+        <v>6929458</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5283,7 +5278,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5293,7 +5288,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5320,7 +5320,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132548541</v>
+        <v>132548574</v>
       </c>
       <c r="B44" t="n">
         <v>92217</v>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530677</v>
+        <v>530833</v>
       </c>
       <c r="R44" t="n">
-        <v>6929443</v>
+        <v>6929513</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132548556</v>
+        <v>132548541</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5438,21 +5438,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530727</v>
+        <v>530677</v>
       </c>
       <c r="R45" t="n">
-        <v>6929373</v>
+        <v>6929443</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5534,32 +5534,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132548553</v>
+        <v>132548556</v>
       </c>
       <c r="B46" t="n">
-        <v>80342</v>
+        <v>91918</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>530693</v>
+        <v>530727</v>
       </c>
       <c r="R46" t="n">
-        <v>6929364</v>
+        <v>6929373</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
